--- a/artfynd/A 3954-2025 artfynd.xlsx
+++ b/artfynd/A 3954-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,38 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56125123</v>
+        <v>81678685</v>
       </c>
       <c r="B2" t="n">
-        <v>101130</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>224409</v>
+        <v>563</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig sandviol</t>
+          <t>Sanddraba</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Viola rupestris subsp. rupestris</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Draba nemorosa</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -716,14 +715,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Västanån, Fråganbo, Upl</t>
+          <t>Västanåvägen, N om Fråganbo, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>633462.8659950662</v>
+        <v>633437</v>
       </c>
       <c r="R2" t="n">
-        <v>6720131.888929284</v>
+        <v>6719998</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,22 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-05-13</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-05-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-05-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-05-10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,59 +781,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>57458485</v>
+        <v>67980988</v>
       </c>
       <c r="B3" t="n">
-        <v>106707</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>88424</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220204</v>
+        <v>1008</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Igelkottsröksvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Lycoperdon echinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>NV Golfbanan 1, Upl</t>
+          <t>Fråganbo, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>633455.1982178107</v>
+        <v>633469</v>
       </c>
       <c r="R3" t="n">
-        <v>6720166.022376963</v>
+        <v>6720185</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,22 +855,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2015-08-03</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1993-08-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2015-08-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1993-08-08</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>foto finns</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,74 +880,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bengt Hemström</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Hemström</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>62000738</v>
+        <v>104065345</v>
       </c>
       <c r="B4" t="n">
-        <v>106707</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220204</v>
+        <v>4392</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Ängsvaxing agg.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Cuphophyllus pratensis s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fråganbo, Upl</t>
+          <t>Västanåvägen 5, Älvkarleby, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>633463.1208653498</v>
+        <v>633546</v>
       </c>
       <c r="R4" t="n">
-        <v>6720125.014791992</v>
+        <v>6720247</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,22 +954,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2016-09-13</t>
+          <t>2022-10-12</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2016-09-13</t>
+          <t>2022-10-12</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,27 +984,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Magnus Stenmark</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Magnus Stenmark</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>61999706</v>
+        <v>56091549</v>
       </c>
       <c r="B5" t="n">
-        <v>99590</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109815</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1050,16 +1007,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221333</v>
+        <v>220204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Backklöver</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Trifolium montanum</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1067,17 +1024,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Fråganbo, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>633465.9819618803</v>
+        <v>633427</v>
       </c>
       <c r="R5" t="n">
-        <v>6720193.956157884</v>
+        <v>6720185</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,27 +1070,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2016-09-13</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2016-09-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>spridd</t>
+          <t>2015-07-11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,59 +1102,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>67980988</v>
+        <v>57458485</v>
       </c>
       <c r="B6" t="n">
-        <v>86860</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109815</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1008</v>
+        <v>220204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Igelkottsröksvamp</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycoperdon echinatum</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fråganbo, Upl</t>
+          <t>NV Golfbanan 1, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>633468.768660692</v>
+        <v>633455</v>
       </c>
       <c r="R6" t="n">
-        <v>6720185.209307346</v>
+        <v>6720166</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,27 +1176,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1993-08-08</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1993-08-08</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>foto finns</t>
+          <t>2015-08-03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,27 +1196,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Bengt Hemström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Bengt Hemström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>81678866</v>
+        <v>62000738</v>
       </c>
       <c r="B7" t="n">
-        <v>101132</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109815</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1293,22 +1219,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>224412</v>
+        <v>220204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hårig sandviol</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Viola rupestris var. rupestris</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1318,14 +1248,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Västanåvägen, N om Fråganbo, Upl</t>
+          <t>Fråganbo, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>633454.9248629587</v>
+        <v>633463</v>
       </c>
       <c r="R7" t="n">
-        <v>6720160.112082355</v>
+        <v>6720125</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1352,22 +1282,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2019-05-05</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2019-05-05</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1387,22 +1307,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Tommy Löfgren, Oskar Löfgren</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>81678922</v>
+        <v>61999706</v>
       </c>
       <c r="B8" t="n">
-        <v>97952</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1410,43 +1325,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222617</v>
+        <v>221333</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Flentimotej</t>
+          <t>Backklöver</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phleum phleoides</t>
+          <t>Trifolium montanum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) H. Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Fråganbo, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>633473.2494781645</v>
+        <v>633466</v>
       </c>
       <c r="R8" t="n">
-        <v>6720183.90042282</v>
+        <v>6720194</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1473,22 +1379,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2019-08-14</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2019-08-14</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-13</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>spridd</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1515,15 +1416,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>88767662</v>
+        <v>121124886</v>
       </c>
       <c r="B9" t="n">
-        <v>101132</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,22 +1427,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>224412</v>
+        <v>221333</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hårig sandviol</t>
+          <t>Backklöver</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Viola rupestris var. rupestris</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Trifolium montanum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1556,14 +1456,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fråganbo, Upl</t>
+          <t>Fråganbo, norr om, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>633443.8695561663</v>
+        <v>633473</v>
       </c>
       <c r="R9" t="n">
-        <v>6720205.919880949</v>
+        <v>6720182</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1590,22 +1490,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2020-05-11</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2020-05-11</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>torräng på strandvall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1632,55 +1527,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>88767663</v>
+        <v>113529832</v>
       </c>
       <c r="B10" t="n">
-        <v>101132</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>224412</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hårig sandviol</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Viola rupestris var. rupestris</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fråganbo, Upl</t>
+          <t>Gävle_Älvkarleby, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633458.2060959976</v>
+        <v>633636</v>
       </c>
       <c r="R10" t="n">
-        <v>6720284.135082964</v>
+        <v>6720357</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1707,22 +1592,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2020-05-11</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2020-05-11</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-01</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Calluna_AB</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1737,67 +1617,61 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Tom Brodin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Tom Brodin, Magnus Stenmark</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>AKE0012 Kompletterande NVI del 2</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>88767661</v>
+        <v>113280078</v>
       </c>
       <c r="B11" t="n">
-        <v>101132</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>224412</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hårig sandviol</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Viola rupestris var. rupestris</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fråganbo, Upl</t>
+          <t>Hundskogen, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>633435.9072380734</v>
+        <v>633971</v>
       </c>
       <c r="R11" t="n">
-        <v>6720115.155561852</v>
+        <v>6720583</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1824,22 +1698,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2020-05-11</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2020-05-11</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1854,62 +1718,70 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Tom Brodin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Elin Lönnberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113529832</v>
+        <v>81678922</v>
       </c>
       <c r="B12" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100798</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>222617</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Flentimotej</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phleum phleoides</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) H. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gävle_Älvkarleby, Upl</t>
+          <t>Fråganbo, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633636</v>
+        <v>633473</v>
       </c>
       <c r="R12" t="n">
-        <v>6720357</v>
+        <v>6720184</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1936,17 +1808,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2019-08-14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Calluna_AB</t>
+          <t>2019-08-14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1961,31 +1828,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Tom Brodin</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tom Brodin, Magnus Stenmark</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>AKE0012 Kompletterande NVI del 2</t>
-        </is>
-      </c>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121124886</v>
+        <v>121124861</v>
       </c>
       <c r="B13" t="n">
-        <v>101466</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100798</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1993,26 +1851,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221333</v>
+        <v>222617</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Backklöver</t>
+          <t>Flentimotej</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Trifolium montanum</t>
+          <t>Phleum phleoides</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) H. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2026,10 +1884,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>633473</v>
+        <v>633467</v>
       </c>
       <c r="R13" t="n">
-        <v>6720182</v>
+        <v>6720171</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2093,15 +1951,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121124861</v>
+        <v>56125123</v>
       </c>
       <c r="B14" t="n">
-        <v>99758</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103693</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2109,26 +1962,22 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222617</v>
+        <v>224409</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Flentimotej</t>
+          <t>Vanlig sandviol</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phleum phleoides</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(L.) H. Karst.</t>
-        </is>
-      </c>
+          <t>Viola rupestris subsp. rupestris</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2138,14 +1987,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fråganbo, norr om, Upl</t>
+          <t>Västanån, Fråganbo, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>633467</v>
+        <v>633463</v>
       </c>
       <c r="R14" t="n">
-        <v>6720171</v>
+        <v>6720132</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2172,17 +2021,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2014-05-13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>torräng på strandvall</t>
+          <t>2014-05-13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2206,6 +2050,1239 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>81678849</v>
+      </c>
+      <c r="B15" t="n">
+        <v>103695</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>224412</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Hårig sandviol</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Viola rupestris var. rupestris</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Västanåvägen, N om Fråganbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>633434</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6720198</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2019-05-10</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2019-05-10</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>81678851</v>
+      </c>
+      <c r="B16" t="n">
+        <v>103695</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>224412</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Hårig sandviol</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Viola rupestris var. rupestris</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Västanåvägen, N om Fråganbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>633428</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6720089</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2019-05-10</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2019-05-10</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>81678852</v>
+      </c>
+      <c r="B17" t="n">
+        <v>103695</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>224412</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Hårig sandviol</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Viola rupestris var. rupestris</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Västanåvägen, N om Fråganbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>633423</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6720184</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2019-05-10</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2019-05-10</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>81678853</v>
+      </c>
+      <c r="B18" t="n">
+        <v>103695</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>224412</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Hårig sandviol</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Viola rupestris var. rupestris</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Västanåvägen, N om Fråganbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>633412</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6720011</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2019-05-10</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2019-05-10</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>81678854</v>
+      </c>
+      <c r="B19" t="n">
+        <v>103695</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>224412</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Hårig sandviol</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Viola rupestris var. rupestris</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Västanåvägen, N om Fråganbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>633402</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6720040</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2019-05-10</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2019-05-10</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>81678866</v>
+      </c>
+      <c r="B20" t="n">
+        <v>103695</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>224412</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Hårig sandviol</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Viola rupestris var. rupestris</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Västanåvägen, N om Fråganbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>633455</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6720160</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2019-05-05</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2019-05-05</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren, Oskar Löfgren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>88767661</v>
+      </c>
+      <c r="B21" t="n">
+        <v>103695</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>224412</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Hårig sandviol</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Viola rupestris var. rupestris</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Fråganbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>633436</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6720115</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2020-05-11</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2020-05-11</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>88767662</v>
+      </c>
+      <c r="B22" t="n">
+        <v>103695</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>224412</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Hårig sandviol</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Viola rupestris var. rupestris</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Fråganbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>633444</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6720206</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2020-05-11</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2020-05-11</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>88767663</v>
+      </c>
+      <c r="B23" t="n">
+        <v>103695</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>224412</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Hårig sandviol</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Viola rupestris var. rupestris</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Fråganbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>633458</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6720284</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2020-05-11</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2020-05-11</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>88767664</v>
+      </c>
+      <c r="B24" t="n">
+        <v>103695</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>224412</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Hårig sandviol</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Viola rupestris var. rupestris</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Fråganbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>633425</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6720200</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2020-05-11</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2020-05-11</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>88767665</v>
+      </c>
+      <c r="B25" t="n">
+        <v>103695</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>224412</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Hårig sandviol</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Viola rupestris var. rupestris</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Fråganbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>633428</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6720153</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2020-05-11</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2020-05-11</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>67980948</v>
+      </c>
+      <c r="B26" t="n">
+        <v>82979</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>259326</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Rödbrun jordtunga</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Microglossum fuscorubens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Boud.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Fråganbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>633465</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6720113</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2017-09-25</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2017-09-25</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>foto</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3954-2025 artfynd.xlsx
+++ b/artfynd/A 3954-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81678685</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67980988</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104065345</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1099,6 +1119,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091549</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1205,6 +1230,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57458485</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1311,6 +1341,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62000738</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1413,6 +1448,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61999706</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1524,6 +1564,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124886</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1630,6 +1675,11 @@
           <t>AKE0012 Kompletterande NVI del 2</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113529832</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1731,6 +1781,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280078</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1837,6 +1892,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81678922</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1948,6 +2008,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124861</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2050,6 +2115,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56125123</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2152,6 +2222,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81678849</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2254,6 +2329,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81678851</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2356,6 +2436,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81678852</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2458,6 +2543,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81678853</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2560,6 +2650,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81678854</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2662,6 +2757,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81678866</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2764,6 +2864,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88767661</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2866,6 +2971,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88767662</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2968,6 +3078,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88767663</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3070,6 +3185,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88767664</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3172,6 +3292,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88767665</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3283,8 +3408,40 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67980948</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>